--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123957406</v>
+        <v>123957350</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>91010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,58 +691,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Kapellskär, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623479</v>
+        <v>623413</v>
       </c>
       <c r="R2" t="n">
-        <v>6749283</v>
+        <v>6749307</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,19 +759,9 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-10</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,18 +770,54 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Fruktkropparna ca 10 meter upp</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Fruktkropparna ca 10 meter upp</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123957350</v>
+        <v>123957406</v>
       </c>
       <c r="B3" t="n">
-        <v>91010</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,45 +830,58 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kapellskär, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623413</v>
+        <v>623479</v>
       </c>
       <c r="R3" t="n">
-        <v>6749307</v>
+        <v>6749283</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -885,9 +911,19 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -896,36 +932,20 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Fruktkropparna ca 10 meter upp</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Fruktkropparna ca 10 meter upp</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
       <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123957350</v>
+        <v>123957406</v>
       </c>
       <c r="B2" t="n">
-        <v>91010</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,45 +691,58 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kapellskär, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623413</v>
+        <v>623479</v>
       </c>
       <c r="R2" t="n">
-        <v>6749307</v>
+        <v>6749283</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,45 +772,29 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Fruktkropparna ca 10 meter upp</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Fruktkropparna ca 10 meter upp</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -814,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123957406</v>
+        <v>123957350</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
+        <v>91010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,58 +827,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Kapellskär, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623479</v>
+        <v>623413</v>
       </c>
       <c r="R3" t="n">
-        <v>6749283</v>
+        <v>6749307</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -911,29 +895,45 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Fruktkropparna ca 10 meter upp</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Fruktkropparna ca 10 meter upp</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -947,6 +947,2705 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>124081970</v>
+      </c>
+      <c r="B4" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Homaren, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>623294</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6749289</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>124082242</v>
+      </c>
+      <c r="B5" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>623464</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6749273</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124082466</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Homaren, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>623332</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6749186</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>124082364</v>
+      </c>
+      <c r="B7" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>623436</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6749241</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>124082656</v>
+      </c>
+      <c r="B8" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Homaren, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>623245</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6749178</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>124082081</v>
+      </c>
+      <c r="B9" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Homaren, Gstr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>623367</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6749289</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>124081914</v>
+      </c>
+      <c r="B10" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Homaren, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>623277</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6749287</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>124082534</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Homaren, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>623302</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6749172</v>
+      </c>
+      <c r="S11" t="n">
+        <v>5</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>124082802</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Homaren, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>623221</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6749218</v>
+      </c>
+      <c r="S12" t="n">
+        <v>5</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>124082323</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>623457</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6749259</v>
+      </c>
+      <c r="S13" t="n">
+        <v>5</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>124082677</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Homaren, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>623221</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6749177</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>124082290</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>623462</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6749264</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>124082507</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Homaren, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>623312</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6749173</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>124082864</v>
+      </c>
+      <c r="B17" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Vreten, Säljemar, Gstr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>623224</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6749226</v>
+      </c>
+      <c r="S17" t="n">
+        <v>5</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>124082776</v>
+      </c>
+      <c r="B18" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Homaren, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>623214</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6749211</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>124081656</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79869</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Homaren, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>623335</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6749272</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>124081547</v>
+      </c>
+      <c r="B20" t="n">
+        <v>91008</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Homaren, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>623297</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6749278</v>
+      </c>
+      <c r="S20" t="n">
+        <v>5</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>12:30</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>124082422</v>
+      </c>
+      <c r="B21" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>623429</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6749238</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>124082629</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Homaren, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>623266</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6749179</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>124081858</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Homaren, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>623259</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6749292</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>124082731</v>
+      </c>
+      <c r="B24" t="n">
+        <v>98079</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Homaren, Säljemar Södra, Gstr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>623207</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6749191</v>
+      </c>
+      <c r="S24" t="n">
+        <v>5</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gävle</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gästrikland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Hille</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Petter  Hillborg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123957406</v>
+        <v>123957350</v>
       </c>
       <c r="B2" t="n">
-        <v>57491</v>
+        <v>91010</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,58 +691,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Kapellskär, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623479</v>
+        <v>623413</v>
       </c>
       <c r="R2" t="n">
-        <v>6749283</v>
+        <v>6749307</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,29 +759,45 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Fruktkropparna ca 10 meter upp</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Fruktkropparna ca 10 meter upp</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -811,10 +814,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123957350</v>
+        <v>123957406</v>
       </c>
       <c r="B3" t="n">
-        <v>91010</v>
+        <v>57491</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -827,45 +830,58 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kapellskär, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623413</v>
+        <v>623479</v>
       </c>
       <c r="R3" t="n">
-        <v>6749307</v>
+        <v>6749283</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -895,45 +911,29 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Fruktkropparna ca 10 meter upp</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Fruktkropparna ca 10 meter upp</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -950,7 +950,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124081970</v>
+        <v>124082364</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1002,14 +1002,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623294</v>
+        <v>623436</v>
       </c>
       <c r="R4" t="n">
-        <v>6749289</v>
+        <v>6749241</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124082242</v>
+        <v>124082802</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1131,14 +1131,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623464</v>
+        <v>623221</v>
       </c>
       <c r="R5" t="n">
-        <v>6749273</v>
+        <v>6749218</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1208,7 +1208,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124082466</v>
+        <v>124082656</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623332</v>
+        <v>623245</v>
       </c>
       <c r="R6" t="n">
-        <v>6749186</v>
+        <v>6749178</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124082364</v>
+        <v>124082242</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1393,10 +1393,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623436</v>
+        <v>623464</v>
       </c>
       <c r="R7" t="n">
-        <v>6749241</v>
+        <v>6749273</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124082656</v>
+        <v>124082466</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623245</v>
+        <v>623332</v>
       </c>
       <c r="R8" t="n">
-        <v>6749178</v>
+        <v>6749186</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124082081</v>
+        <v>124082864</v>
       </c>
       <c r="B9" t="n">
         <v>98079</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1647,14 +1647,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Homaren, Gstr</t>
+          <t>Vreten, Säljemar, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623367</v>
+        <v>623224</v>
       </c>
       <c r="R9" t="n">
-        <v>6749289</v>
+        <v>6749226</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1686,7 +1686,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1724,7 +1724,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124081914</v>
+        <v>124082731</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1780,10 +1780,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623277</v>
+        <v>623207</v>
       </c>
       <c r="R10" t="n">
-        <v>6749287</v>
+        <v>6749191</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1853,7 +1853,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124082534</v>
+        <v>124082776</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1888,7 +1888,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1909,10 +1909,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623302</v>
+        <v>623214</v>
       </c>
       <c r="R11" t="n">
-        <v>6749172</v>
+        <v>6749211</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1982,7 +1982,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124082802</v>
+        <v>124082629</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -2017,7 +2017,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2038,10 +2038,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623221</v>
+        <v>623266</v>
       </c>
       <c r="R12" t="n">
-        <v>6749218</v>
+        <v>6749179</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2240,7 +2240,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124082677</v>
+        <v>124081970</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2275,7 +2275,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2296,10 +2296,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623221</v>
+        <v>623294</v>
       </c>
       <c r="R14" t="n">
-        <v>6749177</v>
+        <v>6749289</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2369,7 +2369,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124082290</v>
+        <v>124082507</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2421,14 +2421,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623462</v>
+        <v>623312</v>
       </c>
       <c r="R15" t="n">
-        <v>6749264</v>
+        <v>6749173</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2498,7 +2498,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124082507</v>
+        <v>124082677</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623312</v>
+        <v>623221</v>
       </c>
       <c r="R16" t="n">
-        <v>6749173</v>
+        <v>6749177</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2627,7 +2627,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124082864</v>
+        <v>124082422</v>
       </c>
       <c r="B17" t="n">
         <v>98079</v>
@@ -2679,14 +2679,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vreten, Säljemar, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623224</v>
+        <v>623429</v>
       </c>
       <c r="R17" t="n">
-        <v>6749226</v>
+        <v>6749238</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2718,17 +2718,17 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>12:00</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2756,7 +2756,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124082776</v>
+        <v>124081858</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2791,7 +2791,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2812,10 +2812,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623214</v>
+        <v>623259</v>
       </c>
       <c r="R18" t="n">
-        <v>6749211</v>
+        <v>6749292</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2857,7 +2857,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2885,10 +2885,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124081656</v>
+        <v>124082290</v>
       </c>
       <c r="B19" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2897,49 +2897,54 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623335</v>
+        <v>623462</v>
       </c>
       <c r="R19" t="n">
-        <v>6749272</v>
+        <v>6749264</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2981,7 +2986,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3009,10 +3014,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124081547</v>
+        <v>124081656</v>
       </c>
       <c r="B20" t="n">
-        <v>91008</v>
+        <v>79869</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3025,31 +3030,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5432</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -3060,10 +3065,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623297</v>
+        <v>623335</v>
       </c>
       <c r="R20" t="n">
-        <v>6749278</v>
+        <v>6749272</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3090,22 +3095,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3133,7 +3138,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124082422</v>
+        <v>124081914</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -3168,7 +3173,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3185,14 +3190,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623429</v>
+        <v>623277</v>
       </c>
       <c r="R21" t="n">
-        <v>6749238</v>
+        <v>6749287</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3262,7 +3267,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124082629</v>
+        <v>124082534</v>
       </c>
       <c r="B22" t="n">
         <v>98079</v>
@@ -3297,7 +3302,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3318,10 +3323,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623266</v>
+        <v>623302</v>
       </c>
       <c r="R22" t="n">
-        <v>6749179</v>
+        <v>6749172</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3391,7 +3396,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124081858</v>
+        <v>124082081</v>
       </c>
       <c r="B23" t="n">
         <v>98079</v>
@@ -3426,7 +3431,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3443,14 +3448,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Homaren, Gstr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623259</v>
+        <v>623367</v>
       </c>
       <c r="R23" t="n">
-        <v>6749292</v>
+        <v>6749289</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3492,7 +3497,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3520,10 +3525,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124082731</v>
+        <v>124081547</v>
       </c>
       <c r="B24" t="n">
-        <v>98079</v>
+        <v>91008</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3532,43 +3537,38 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623207</v>
+        <v>623297</v>
       </c>
       <c r="R24" t="n">
-        <v>6749191</v>
+        <v>6749278</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3606,22 +3606,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -2885,10 +2885,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124082290</v>
+        <v>124081656</v>
       </c>
       <c r="B19" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2897,54 +2897,49 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623462</v>
+        <v>623335</v>
       </c>
       <c r="R19" t="n">
-        <v>6749264</v>
+        <v>6749272</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2986,7 +2981,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3014,10 +3009,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124081656</v>
+        <v>124082290</v>
       </c>
       <c r="B20" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -3026,49 +3021,54 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623335</v>
+        <v>623462</v>
       </c>
       <c r="R20" t="n">
-        <v>6749272</v>
+        <v>6749264</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3110,7 +3110,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3396,10 +3396,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124082081</v>
+        <v>124081547</v>
       </c>
       <c r="B23" t="n">
-        <v>98079</v>
+        <v>91008</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3408,54 +3408,49 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Homaren, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623367</v>
+        <v>623297</v>
       </c>
       <c r="R23" t="n">
-        <v>6749289</v>
+        <v>6749278</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3482,22 +3477,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3525,10 +3520,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124081547</v>
+        <v>124082081</v>
       </c>
       <c r="B24" t="n">
-        <v>91008</v>
+        <v>98079</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3537,49 +3532,54 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Homaren, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623297</v>
+        <v>623367</v>
       </c>
       <c r="R24" t="n">
-        <v>6749278</v>
+        <v>6749289</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3606,22 +3606,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123957350</v>
+        <v>123957406</v>
       </c>
       <c r="B2" t="n">
-        <v>91010</v>
+        <v>57491</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,45 +691,58 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kapellskär, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623413</v>
+        <v>623479</v>
       </c>
       <c r="R2" t="n">
-        <v>6749307</v>
+        <v>6749283</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,45 +772,29 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Fruktkropparna ca 10 meter upp</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Fruktkropparna ca 10 meter upp</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -814,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123957406</v>
+        <v>123957350</v>
       </c>
       <c r="B3" t="n">
-        <v>57491</v>
+        <v>91010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,58 +827,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Kapellskär, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623479</v>
+        <v>623413</v>
       </c>
       <c r="R3" t="n">
-        <v>6749283</v>
+        <v>6749307</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -911,29 +895,45 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Fruktkropparna ca 10 meter upp</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Fruktkropparna ca 10 meter upp</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -950,7 +950,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124082364</v>
+        <v>124082656</v>
       </c>
       <c r="B4" t="n">
         <v>98079</v>
@@ -1002,14 +1002,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623436</v>
+        <v>623245</v>
       </c>
       <c r="R4" t="n">
-        <v>6749241</v>
+        <v>6749178</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124082802</v>
+        <v>124081970</v>
       </c>
       <c r="B5" t="n">
         <v>98079</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623221</v>
+        <v>623294</v>
       </c>
       <c r="R5" t="n">
-        <v>6749218</v>
+        <v>6749289</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1208,7 +1208,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124082656</v>
+        <v>124082507</v>
       </c>
       <c r="B6" t="n">
         <v>98079</v>
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623245</v>
+        <v>623312</v>
       </c>
       <c r="R6" t="n">
-        <v>6749178</v>
+        <v>6749173</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124082242</v>
+        <v>124082629</v>
       </c>
       <c r="B7" t="n">
         <v>98079</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1389,14 +1389,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623464</v>
+        <v>623266</v>
       </c>
       <c r="R7" t="n">
-        <v>6749273</v>
+        <v>6749179</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1466,7 +1466,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124082466</v>
+        <v>124082364</v>
       </c>
       <c r="B8" t="n">
         <v>98079</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1518,14 +1518,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623332</v>
+        <v>623436</v>
       </c>
       <c r="R8" t="n">
-        <v>6749186</v>
+        <v>6749241</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1595,10 +1595,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124082864</v>
+        <v>124081547</v>
       </c>
       <c r="B9" t="n">
-        <v>98079</v>
+        <v>91008</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1607,54 +1607,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Vreten, Säljemar, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623224</v>
+        <v>623297</v>
       </c>
       <c r="R9" t="n">
-        <v>6749226</v>
+        <v>6749278</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1681,17 +1676,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -1724,7 +1719,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124082731</v>
+        <v>124082290</v>
       </c>
       <c r="B10" t="n">
         <v>98079</v>
@@ -1776,14 +1771,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623207</v>
+        <v>623462</v>
       </c>
       <c r="R10" t="n">
-        <v>6749191</v>
+        <v>6749264</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1853,7 +1848,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124082776</v>
+        <v>124082864</v>
       </c>
       <c r="B11" t="n">
         <v>98079</v>
@@ -1905,14 +1900,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Vreten, Säljemar, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623214</v>
+        <v>623224</v>
       </c>
       <c r="R11" t="n">
-        <v>6749211</v>
+        <v>6749226</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1944,7 +1939,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1954,7 +1949,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1982,7 +1977,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124082629</v>
+        <v>124082802</v>
       </c>
       <c r="B12" t="n">
         <v>98079</v>
@@ -2017,7 +2012,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2038,10 +2033,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623266</v>
+        <v>623221</v>
       </c>
       <c r="R12" t="n">
-        <v>6749179</v>
+        <v>6749218</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2240,7 +2235,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124081970</v>
+        <v>124082081</v>
       </c>
       <c r="B14" t="n">
         <v>98079</v>
@@ -2275,7 +2270,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2292,11 +2287,11 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Homaren, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623294</v>
+        <v>623367</v>
       </c>
       <c r="R14" t="n">
         <v>6749289</v>
@@ -2369,7 +2364,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124082507</v>
+        <v>124082534</v>
       </c>
       <c r="B15" t="n">
         <v>98079</v>
@@ -2404,7 +2399,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2425,10 +2420,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623312</v>
+        <v>623302</v>
       </c>
       <c r="R15" t="n">
-        <v>6749173</v>
+        <v>6749172</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2498,7 +2493,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124082677</v>
+        <v>124082242</v>
       </c>
       <c r="B16" t="n">
         <v>98079</v>
@@ -2550,14 +2545,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623221</v>
+        <v>623464</v>
       </c>
       <c r="R16" t="n">
-        <v>6749177</v>
+        <v>6749273</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2756,7 +2751,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124081858</v>
+        <v>124082776</v>
       </c>
       <c r="B18" t="n">
         <v>98079</v>
@@ -2791,7 +2786,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2812,10 +2807,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623259</v>
+        <v>623214</v>
       </c>
       <c r="R18" t="n">
-        <v>6749292</v>
+        <v>6749211</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2857,7 +2852,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2885,10 +2880,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124081656</v>
+        <v>124081858</v>
       </c>
       <c r="B19" t="n">
-        <v>79869</v>
+        <v>98079</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2897,38 +2892,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2936,10 +2936,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623335</v>
+        <v>623259</v>
       </c>
       <c r="R19" t="n">
-        <v>6749272</v>
+        <v>6749292</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3009,7 +3009,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124082290</v>
+        <v>124082677</v>
       </c>
       <c r="B20" t="n">
         <v>98079</v>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3061,14 +3061,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623462</v>
+        <v>623221</v>
       </c>
       <c r="R20" t="n">
-        <v>6749264</v>
+        <v>6749177</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3138,7 +3138,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124081914</v>
+        <v>124082731</v>
       </c>
       <c r="B21" t="n">
         <v>98079</v>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3194,10 +3194,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623277</v>
+        <v>623207</v>
       </c>
       <c r="R21" t="n">
-        <v>6749287</v>
+        <v>6749191</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3267,10 +3267,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124082534</v>
+        <v>124081656</v>
       </c>
       <c r="B22" t="n">
-        <v>98079</v>
+        <v>79869</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3279,43 +3279,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3323,10 +3318,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623302</v>
+        <v>623335</v>
       </c>
       <c r="R22" t="n">
-        <v>6749172</v>
+        <v>6749272</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3368,7 +3363,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3396,10 +3391,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124081547</v>
+        <v>124082466</v>
       </c>
       <c r="B23" t="n">
-        <v>91008</v>
+        <v>98079</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3408,38 +3403,43 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623297</v>
+        <v>623332</v>
       </c>
       <c r="R23" t="n">
-        <v>6749278</v>
+        <v>6749186</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3477,22 +3477,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3520,7 +3520,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124082081</v>
+        <v>124081914</v>
       </c>
       <c r="B24" t="n">
         <v>98079</v>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3572,14 +3572,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Homaren, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623367</v>
+        <v>623277</v>
       </c>
       <c r="R24" t="n">
-        <v>6749289</v>
+        <v>6749287</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -950,7 +950,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124082466</v>
+        <v>124082290</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1002,14 +1002,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623332</v>
+        <v>623462</v>
       </c>
       <c r="R4" t="n">
-        <v>6749186</v>
+        <v>6749264</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124082629</v>
+        <v>124082422</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,14 +1131,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623266</v>
+        <v>623429</v>
       </c>
       <c r="R5" t="n">
-        <v>6749179</v>
+        <v>6749238</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1208,7 +1208,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124082290</v>
+        <v>124081970</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1260,14 +1260,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623462</v>
+        <v>623294</v>
       </c>
       <c r="R6" t="n">
-        <v>6749264</v>
+        <v>6749289</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124081970</v>
+        <v>124082864</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1389,14 +1389,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Vreten, Säljemar, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623294</v>
+        <v>623224</v>
       </c>
       <c r="R7" t="n">
-        <v>6749289</v>
+        <v>6749226</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1428,7 +1428,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1466,10 +1466,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124081656</v>
+        <v>124082731</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1478,38 +1478,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1517,10 +1522,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623335</v>
+        <v>623207</v>
       </c>
       <c r="R8" t="n">
-        <v>6749272</v>
+        <v>6749191</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1562,7 +1567,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1590,7 +1595,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124081914</v>
+        <v>124082081</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1625,7 +1630,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1642,14 +1647,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Homaren, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623277</v>
+        <v>623367</v>
       </c>
       <c r="R9" t="n">
-        <v>6749287</v>
+        <v>6749289</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1719,7 +1724,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124082507</v>
+        <v>124082323</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1754,7 +1759,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1771,14 +1776,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623312</v>
+        <v>623457</v>
       </c>
       <c r="R10" t="n">
-        <v>6749173</v>
+        <v>6749259</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1848,7 +1853,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124082731</v>
+        <v>124082677</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1883,7 +1888,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1904,10 +1909,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623207</v>
+        <v>623221</v>
       </c>
       <c r="R11" t="n">
-        <v>6749191</v>
+        <v>6749177</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2106,7 +2111,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124082081</v>
+        <v>124081858</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2141,7 +2146,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2158,14 +2163,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Homaren, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623367</v>
+        <v>623259</v>
       </c>
       <c r="R13" t="n">
-        <v>6749289</v>
+        <v>6749292</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2207,7 +2212,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2235,10 +2240,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124081858</v>
+        <v>124081547</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2247,43 +2252,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2291,10 +2291,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623259</v>
+        <v>623297</v>
       </c>
       <c r="R14" t="n">
-        <v>6749292</v>
+        <v>6749278</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2321,22 +2321,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2364,7 +2364,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124082864</v>
+        <v>124081914</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2416,14 +2416,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Vreten, Säljemar, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623224</v>
+        <v>623277</v>
       </c>
       <c r="R15" t="n">
-        <v>6749226</v>
+        <v>6749287</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2455,17 +2455,17 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
           <t>12:00</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2493,7 +2493,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124082656</v>
+        <v>124082242</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2528,7 +2528,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2545,14 +2545,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623245</v>
+        <v>623464</v>
       </c>
       <c r="R16" t="n">
-        <v>6749178</v>
+        <v>6749273</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2622,7 +2622,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124082534</v>
+        <v>124082629</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2678,10 +2678,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623302</v>
+        <v>623266</v>
       </c>
       <c r="R17" t="n">
-        <v>6749172</v>
+        <v>6749179</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2751,7 +2751,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124082422</v>
+        <v>124082364</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2786,7 +2786,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2807,10 +2807,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623429</v>
+        <v>623436</v>
       </c>
       <c r="R18" t="n">
-        <v>6749238</v>
+        <v>6749241</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2880,10 +2880,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124081547</v>
+        <v>124082507</v>
       </c>
       <c r="B19" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2892,38 +2892,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2931,10 +2936,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623297</v>
+        <v>623312</v>
       </c>
       <c r="R19" t="n">
-        <v>6749278</v>
+        <v>6749173</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2961,22 +2966,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -3004,7 +3009,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124082323</v>
+        <v>124082534</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -3039,7 +3044,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3056,14 +3061,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623457</v>
+        <v>623302</v>
       </c>
       <c r="R20" t="n">
-        <v>6749259</v>
+        <v>6749172</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3133,7 +3138,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124082242</v>
+        <v>124082466</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -3185,14 +3190,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623464</v>
+        <v>623332</v>
       </c>
       <c r="R21" t="n">
-        <v>6749273</v>
+        <v>6749186</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3262,10 +3267,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124082802</v>
+        <v>124081656</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3274,43 +3279,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623221</v>
+        <v>623335</v>
       </c>
       <c r="R22" t="n">
-        <v>6749218</v>
+        <v>6749272</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3391,7 +3391,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124082677</v>
+        <v>124082802</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3450,7 +3450,7 @@
         <v>623221</v>
       </c>
       <c r="R23" t="n">
-        <v>6749177</v>
+        <v>6749218</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3520,7 +3520,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124082364</v>
+        <v>124082656</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3572,14 +3572,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623436</v>
+        <v>623245</v>
       </c>
       <c r="R24" t="n">
-        <v>6749241</v>
+        <v>6749178</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -950,7 +950,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124082290</v>
+        <v>124082422</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623462</v>
+        <v>623429</v>
       </c>
       <c r="R4" t="n">
-        <v>6749264</v>
+        <v>6749238</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124082422</v>
+        <v>124082731</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,14 +1131,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623429</v>
+        <v>623207</v>
       </c>
       <c r="R5" t="n">
-        <v>6749238</v>
+        <v>6749191</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1208,7 +1208,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124081970</v>
+        <v>124082776</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623294</v>
+        <v>623214</v>
       </c>
       <c r="R6" t="n">
-        <v>6749289</v>
+        <v>6749211</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124082864</v>
+        <v>124082081</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1389,14 +1389,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Vreten, Säljemar, Gstr</t>
+          <t>Homaren, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623224</v>
+        <v>623367</v>
       </c>
       <c r="R7" t="n">
-        <v>6749226</v>
+        <v>6749289</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1428,17 +1428,17 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
           <t>12:00</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1466,7 +1466,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124082731</v>
+        <v>124082677</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1501,7 +1501,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623207</v>
+        <v>623221</v>
       </c>
       <c r="R8" t="n">
-        <v>6749191</v>
+        <v>6749177</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1595,7 +1595,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124082081</v>
+        <v>124082242</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1647,14 +1647,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Homaren, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623367</v>
+        <v>623464</v>
       </c>
       <c r="R9" t="n">
-        <v>6749289</v>
+        <v>6749273</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1724,10 +1724,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124082323</v>
+        <v>124081547</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,54 +1736,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623457</v>
+        <v>623297</v>
       </c>
       <c r="R10" t="n">
-        <v>6749259</v>
+        <v>6749278</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1810,22 +1805,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1853,7 +1848,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124082677</v>
+        <v>124081970</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1888,7 +1883,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1909,10 +1904,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623221</v>
+        <v>623294</v>
       </c>
       <c r="R11" t="n">
-        <v>6749177</v>
+        <v>6749289</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1982,7 +1977,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124082776</v>
+        <v>124082629</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -2017,7 +2012,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2038,10 +2033,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623214</v>
+        <v>623266</v>
       </c>
       <c r="R12" t="n">
-        <v>6749211</v>
+        <v>6749179</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2111,7 +2106,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124081858</v>
+        <v>124082466</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2146,7 +2141,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2167,10 +2162,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623259</v>
+        <v>623332</v>
       </c>
       <c r="R13" t="n">
-        <v>6749292</v>
+        <v>6749186</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2212,7 +2207,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2240,10 +2235,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124081547</v>
+        <v>124082290</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2252,49 +2247,54 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623297</v>
+        <v>623462</v>
       </c>
       <c r="R14" t="n">
-        <v>6749278</v>
+        <v>6749264</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2321,22 +2321,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2493,10 +2493,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124082242</v>
+        <v>124081656</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2505,54 +2505,49 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623464</v>
+        <v>623335</v>
       </c>
       <c r="R16" t="n">
-        <v>6749273</v>
+        <v>6749272</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2594,7 +2589,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2622,7 +2617,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124082629</v>
+        <v>124082864</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2657,7 +2652,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2674,14 +2669,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Vreten, Säljemar, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623266</v>
+        <v>623224</v>
       </c>
       <c r="R17" t="n">
-        <v>6749179</v>
+        <v>6749226</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2713,7 +2708,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2723,7 +2718,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2751,7 +2746,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124082364</v>
+        <v>124082656</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2803,14 +2798,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623436</v>
+        <v>623245</v>
       </c>
       <c r="R18" t="n">
-        <v>6749241</v>
+        <v>6749178</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2880,7 +2875,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124082507</v>
+        <v>124082323</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2915,7 +2910,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2932,14 +2927,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623312</v>
+        <v>623457</v>
       </c>
       <c r="R19" t="n">
-        <v>6749173</v>
+        <v>6749259</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3009,7 +3004,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124082534</v>
+        <v>124081858</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -3044,7 +3039,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3065,10 +3060,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623302</v>
+        <v>623259</v>
       </c>
       <c r="R20" t="n">
-        <v>6749172</v>
+        <v>6749292</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3110,7 +3105,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3138,7 +3133,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124082466</v>
+        <v>124082802</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -3194,10 +3189,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623332</v>
+        <v>623221</v>
       </c>
       <c r="R21" t="n">
-        <v>6749186</v>
+        <v>6749218</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3267,10 +3262,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124081656</v>
+        <v>124082507</v>
       </c>
       <c r="B22" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3279,38 +3274,43 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3318,10 +3318,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623335</v>
+        <v>623312</v>
       </c>
       <c r="R22" t="n">
-        <v>6749272</v>
+        <v>6749173</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3391,7 +3391,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124082802</v>
+        <v>124082534</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623221</v>
+        <v>623302</v>
       </c>
       <c r="R23" t="n">
-        <v>6749218</v>
+        <v>6749172</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3520,7 +3520,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124082656</v>
+        <v>124082364</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3572,14 +3572,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623245</v>
+        <v>623436</v>
       </c>
       <c r="R24" t="n">
-        <v>6749178</v>
+        <v>6749241</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -950,7 +950,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124082422</v>
+        <v>124082656</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1002,14 +1002,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623429</v>
+        <v>623245</v>
       </c>
       <c r="R4" t="n">
-        <v>6749238</v>
+        <v>6749178</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124082731</v>
+        <v>124081970</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623207</v>
+        <v>623294</v>
       </c>
       <c r="R5" t="n">
-        <v>6749191</v>
+        <v>6749289</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1208,7 +1208,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124082776</v>
+        <v>124082422</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1260,14 +1260,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623214</v>
+        <v>623429</v>
       </c>
       <c r="R6" t="n">
-        <v>6749211</v>
+        <v>6749238</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1337,10 +1337,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124082081</v>
+        <v>124081547</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1349,54 +1349,49 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Homaren, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623367</v>
+        <v>623297</v>
       </c>
       <c r="R7" t="n">
-        <v>6749289</v>
+        <v>6749278</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1423,22 +1418,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1466,7 +1461,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124082677</v>
+        <v>124082864</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1518,14 +1513,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Vreten, Säljemar, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623221</v>
+        <v>623224</v>
       </c>
       <c r="R8" t="n">
-        <v>6749177</v>
+        <v>6749226</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1557,7 +1552,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1567,7 +1562,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1595,7 +1590,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124082242</v>
+        <v>124082081</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1630,7 +1625,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1647,14 +1642,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623464</v>
+        <v>623367</v>
       </c>
       <c r="R9" t="n">
-        <v>6749273</v>
+        <v>6749289</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1724,10 +1719,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124081547</v>
+        <v>124082290</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,49 +1731,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623297</v>
+        <v>623462</v>
       </c>
       <c r="R10" t="n">
-        <v>6749278</v>
+        <v>6749264</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1805,22 +1805,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1848,7 +1848,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124081970</v>
+        <v>124082323</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1900,14 +1900,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623294</v>
+        <v>623457</v>
       </c>
       <c r="R11" t="n">
-        <v>6749289</v>
+        <v>6749259</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124082466</v>
+        <v>124081858</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623332</v>
+        <v>623259</v>
       </c>
       <c r="R13" t="n">
-        <v>6749186</v>
+        <v>6749292</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2207,7 +2207,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2235,7 +2235,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124082290</v>
+        <v>124082466</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2270,7 +2270,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2287,14 +2287,14 @@
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623462</v>
+        <v>623332</v>
       </c>
       <c r="R14" t="n">
-        <v>6749264</v>
+        <v>6749186</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2364,7 +2364,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124081914</v>
+        <v>124082507</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2399,7 +2399,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2420,10 +2420,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623277</v>
+        <v>623312</v>
       </c>
       <c r="R15" t="n">
-        <v>6749287</v>
+        <v>6749173</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2493,10 +2493,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124081656</v>
+        <v>124082776</v>
       </c>
       <c r="B16" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2505,38 +2505,43 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2544,10 +2549,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623335</v>
+        <v>623214</v>
       </c>
       <c r="R16" t="n">
-        <v>6749272</v>
+        <v>6749211</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2589,7 +2594,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2617,7 +2622,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124082864</v>
+        <v>124082364</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2652,7 +2657,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2669,14 +2674,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Vreten, Säljemar, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623224</v>
+        <v>623436</v>
       </c>
       <c r="R17" t="n">
-        <v>6749226</v>
+        <v>6749241</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2708,17 +2713,17 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
           <t>12:00</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2746,7 +2751,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124082656</v>
+        <v>124082802</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2781,7 +2786,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2802,10 +2807,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623245</v>
+        <v>623221</v>
       </c>
       <c r="R18" t="n">
-        <v>6749178</v>
+        <v>6749218</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2875,7 +2880,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124082323</v>
+        <v>124082731</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2910,7 +2915,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2927,14 +2932,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623457</v>
+        <v>623207</v>
       </c>
       <c r="R19" t="n">
-        <v>6749259</v>
+        <v>6749191</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3004,7 +3009,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124081858</v>
+        <v>124081914</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -3039,7 +3044,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3060,10 +3065,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623259</v>
+        <v>623277</v>
       </c>
       <c r="R20" t="n">
-        <v>6749292</v>
+        <v>6749287</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3105,7 +3110,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3133,7 +3138,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124082802</v>
+        <v>124082242</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -3185,14 +3190,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623221</v>
+        <v>623464</v>
       </c>
       <c r="R21" t="n">
-        <v>6749218</v>
+        <v>6749273</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3262,7 +3267,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124082507</v>
+        <v>124082677</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3297,7 +3302,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3318,10 +3323,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623312</v>
+        <v>623221</v>
       </c>
       <c r="R22" t="n">
-        <v>6749173</v>
+        <v>6749177</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3520,10 +3525,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124082364</v>
+        <v>124081656</v>
       </c>
       <c r="B24" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3532,54 +3537,49 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623436</v>
+        <v>623335</v>
       </c>
       <c r="R24" t="n">
-        <v>6749241</v>
+        <v>6749272</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -950,10 +950,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124082656</v>
+        <v>124081656</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -962,43 +962,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623245</v>
+        <v>623335</v>
       </c>
       <c r="R4" t="n">
-        <v>6749178</v>
+        <v>6749272</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1051,7 +1046,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1079,7 +1074,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124081970</v>
+        <v>124081858</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1135,10 +1130,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623294</v>
+        <v>623259</v>
       </c>
       <c r="R5" t="n">
-        <v>6749289</v>
+        <v>6749292</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1180,7 +1175,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1337,10 +1332,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124081547</v>
+        <v>124081970</v>
       </c>
       <c r="B7" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1349,38 +1344,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623297</v>
+        <v>623294</v>
       </c>
       <c r="R7" t="n">
-        <v>6749278</v>
+        <v>6749289</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1461,7 +1461,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124082864</v>
+        <v>124082802</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1513,14 +1513,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Vreten, Säljemar, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623224</v>
+        <v>623221</v>
       </c>
       <c r="R8" t="n">
-        <v>6749226</v>
+        <v>6749218</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1552,17 +1552,17 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
           <t>12:00</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1719,10 +1719,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124082290</v>
+        <v>124081547</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1731,54 +1731,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623462</v>
+        <v>623297</v>
       </c>
       <c r="R10" t="n">
-        <v>6749264</v>
+        <v>6749278</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1805,22 +1800,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1848,7 +1843,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124082323</v>
+        <v>124082731</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1883,7 +1878,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1900,14 +1895,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623457</v>
+        <v>623207</v>
       </c>
       <c r="R11" t="n">
-        <v>6749259</v>
+        <v>6749191</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1977,7 +1972,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124082629</v>
+        <v>124082677</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -2012,7 +2007,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2033,10 +2028,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623266</v>
+        <v>623221</v>
       </c>
       <c r="R12" t="n">
-        <v>6749179</v>
+        <v>6749177</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2106,7 +2101,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124081858</v>
+        <v>124082364</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2141,7 +2136,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2158,14 +2153,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623259</v>
+        <v>623436</v>
       </c>
       <c r="R13" t="n">
-        <v>6749292</v>
+        <v>6749241</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2207,7 +2202,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2235,7 +2230,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124082466</v>
+        <v>124082656</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2270,7 +2265,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2291,10 +2286,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623332</v>
+        <v>623245</v>
       </c>
       <c r="R14" t="n">
-        <v>6749186</v>
+        <v>6749178</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2364,7 +2359,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124082507</v>
+        <v>124082242</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2399,7 +2394,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2416,14 +2411,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623312</v>
+        <v>623464</v>
       </c>
       <c r="R15" t="n">
-        <v>6749173</v>
+        <v>6749273</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2493,7 +2488,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124082776</v>
+        <v>124082629</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2528,7 +2523,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2549,10 +2544,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623214</v>
+        <v>623266</v>
       </c>
       <c r="R16" t="n">
-        <v>6749211</v>
+        <v>6749179</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2622,7 +2617,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124082364</v>
+        <v>124082507</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2674,14 +2669,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623436</v>
+        <v>623312</v>
       </c>
       <c r="R17" t="n">
-        <v>6749241</v>
+        <v>6749173</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2751,7 +2746,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124082802</v>
+        <v>124082864</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2803,14 +2798,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Vreten, Säljemar, Gstr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623221</v>
+        <v>623224</v>
       </c>
       <c r="R18" t="n">
-        <v>6749218</v>
+        <v>6749226</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2842,7 +2837,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2852,7 +2847,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2880,7 +2875,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124082731</v>
+        <v>124082466</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2915,7 +2910,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2936,10 +2931,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623207</v>
+        <v>623332</v>
       </c>
       <c r="R19" t="n">
-        <v>6749191</v>
+        <v>6749186</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3009,7 +3004,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124081914</v>
+        <v>124082323</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -3044,7 +3039,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3061,14 +3056,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623277</v>
+        <v>623457</v>
       </c>
       <c r="R20" t="n">
-        <v>6749287</v>
+        <v>6749259</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3138,7 +3133,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124082242</v>
+        <v>124082290</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -3173,7 +3168,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3194,10 +3189,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623464</v>
+        <v>623462</v>
       </c>
       <c r="R21" t="n">
-        <v>6749273</v>
+        <v>6749264</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3267,7 +3262,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124082677</v>
+        <v>124082534</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3302,7 +3297,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3323,10 +3318,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623221</v>
+        <v>623302</v>
       </c>
       <c r="R22" t="n">
-        <v>6749177</v>
+        <v>6749172</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3396,7 +3391,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124082534</v>
+        <v>124082776</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3431,7 +3426,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3452,10 +3447,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623302</v>
+        <v>623214</v>
       </c>
       <c r="R23" t="n">
-        <v>6749172</v>
+        <v>6749211</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3525,10 +3520,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124081656</v>
+        <v>124081914</v>
       </c>
       <c r="B24" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3537,38 +3532,43 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623335</v>
+        <v>623277</v>
       </c>
       <c r="R24" t="n">
-        <v>6749272</v>
+        <v>6749287</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3621,7 +3621,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD24" t="b">

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -1590,10 +1590,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124082081</v>
+        <v>124081547</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1602,54 +1602,49 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Homaren, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623367</v>
+        <v>623297</v>
       </c>
       <c r="R9" t="n">
-        <v>6749289</v>
+        <v>6749278</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1676,22 +1671,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1719,10 +1714,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124081547</v>
+        <v>124082081</v>
       </c>
       <c r="B10" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1731,49 +1726,54 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Homaren, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623297</v>
+        <v>623367</v>
       </c>
       <c r="R10" t="n">
-        <v>6749278</v>
+        <v>6749289</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1800,22 +1800,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123957350</v>
+        <v>123957406</v>
       </c>
       <c r="B2" t="n">
-        <v>91032</v>
+        <v>57513</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,45 +691,58 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kapellskär, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623413</v>
+        <v>623479</v>
       </c>
       <c r="R2" t="n">
-        <v>6749307</v>
+        <v>6749283</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -759,45 +772,29 @@
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>Fruktkropparna ca 10 meter upp</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Fruktkropparna ca 10 meter upp</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -814,10 +811,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123957406</v>
+        <v>123957350</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>91032</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -830,58 +827,45 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Kapellskär, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623479</v>
+        <v>623413</v>
       </c>
       <c r="R3" t="n">
-        <v>6749283</v>
+        <v>6749307</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -911,29 +895,45 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>Fruktkropparna ca 10 meter upp</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Fruktkropparna ca 10 meter upp</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -950,10 +950,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124081656</v>
+        <v>124082081</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -962,49 +962,54 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Homaren, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623335</v>
+        <v>623367</v>
       </c>
       <c r="R4" t="n">
-        <v>6749272</v>
+        <v>6749289</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1046,7 +1051,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1074,7 +1079,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124081858</v>
+        <v>124082864</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1109,7 +1114,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1126,14 +1131,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Vreten, Säljemar, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623259</v>
+        <v>623224</v>
       </c>
       <c r="R5" t="n">
-        <v>6749292</v>
+        <v>6749226</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1165,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1175,7 +1180,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1203,7 +1208,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124082422</v>
+        <v>124082507</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1238,7 +1243,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1255,14 +1260,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623429</v>
+        <v>623312</v>
       </c>
       <c r="R6" t="n">
-        <v>6749238</v>
+        <v>6749173</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1332,7 +1337,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124081970</v>
+        <v>124081914</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1367,7 +1372,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1388,10 +1393,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623294</v>
+        <v>623277</v>
       </c>
       <c r="R7" t="n">
-        <v>6749289</v>
+        <v>6749287</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1461,10 +1466,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124082802</v>
+        <v>124081547</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1473,43 +1478,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1517,10 +1517,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623221</v>
+        <v>623297</v>
       </c>
       <c r="R8" t="n">
-        <v>6749218</v>
+        <v>6749278</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1547,22 +1547,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1590,10 +1590,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124081547</v>
+        <v>124082466</v>
       </c>
       <c r="B9" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1602,38 +1602,43 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1641,10 +1646,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623297</v>
+        <v>623332</v>
       </c>
       <c r="R9" t="n">
-        <v>6749278</v>
+        <v>6749186</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1671,22 +1676,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1714,7 +1719,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124082081</v>
+        <v>124082290</v>
       </c>
       <c r="B10" t="n">
         <v>98101</v>
@@ -1766,14 +1771,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Homaren, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623367</v>
+        <v>623462</v>
       </c>
       <c r="R10" t="n">
-        <v>6749289</v>
+        <v>6749264</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1843,10 +1848,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124082731</v>
+        <v>124081656</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1855,43 +1860,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1899,10 +1899,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623207</v>
+        <v>623335</v>
       </c>
       <c r="R11" t="n">
-        <v>6749191</v>
+        <v>6749272</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1972,7 +1972,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124082677</v>
+        <v>124082364</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -2007,7 +2007,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -2024,14 +2024,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623221</v>
+        <v>623436</v>
       </c>
       <c r="R12" t="n">
-        <v>6749177</v>
+        <v>6749241</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2101,7 +2101,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124082364</v>
+        <v>124082323</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2136,7 +2136,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2157,10 +2157,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623436</v>
+        <v>623457</v>
       </c>
       <c r="R13" t="n">
-        <v>6749241</v>
+        <v>6749259</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2230,7 +2230,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124082656</v>
+        <v>124082802</v>
       </c>
       <c r="B14" t="n">
         <v>98101</v>
@@ -2265,7 +2265,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623245</v>
+        <v>623221</v>
       </c>
       <c r="R14" t="n">
-        <v>6749178</v>
+        <v>6749218</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2359,7 +2359,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124082242</v>
+        <v>124082677</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2411,14 +2411,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623464</v>
+        <v>623221</v>
       </c>
       <c r="R15" t="n">
-        <v>6749273</v>
+        <v>6749177</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124082629</v>
+        <v>124081858</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623266</v>
+        <v>623259</v>
       </c>
       <c r="R16" t="n">
-        <v>6749179</v>
+        <v>6749292</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2617,7 +2617,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124082507</v>
+        <v>124082656</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2673,10 +2673,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623312</v>
+        <v>623245</v>
       </c>
       <c r="R17" t="n">
-        <v>6749173</v>
+        <v>6749178</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124082864</v>
+        <v>124082629</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2798,14 +2798,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Vreten, Säljemar, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623224</v>
+        <v>623266</v>
       </c>
       <c r="R18" t="n">
-        <v>6749226</v>
+        <v>6749179</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2837,17 +2837,17 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
           <t>12:00</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2875,7 +2875,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124082466</v>
+        <v>124081970</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2931,10 +2931,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623332</v>
+        <v>623294</v>
       </c>
       <c r="R19" t="n">
-        <v>6749186</v>
+        <v>6749289</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3004,7 +3004,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124082323</v>
+        <v>124082242</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -3060,10 +3060,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623457</v>
+        <v>623464</v>
       </c>
       <c r="R20" t="n">
-        <v>6749259</v>
+        <v>6749273</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3133,7 +3133,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124082290</v>
+        <v>124082776</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3185,14 +3185,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623462</v>
+        <v>623214</v>
       </c>
       <c r="R21" t="n">
-        <v>6749264</v>
+        <v>6749211</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3262,7 +3262,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124082534</v>
+        <v>124082422</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3314,14 +3314,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623302</v>
+        <v>623429</v>
       </c>
       <c r="R22" t="n">
-        <v>6749172</v>
+        <v>6749238</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124082776</v>
+        <v>124082534</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623214</v>
+        <v>623302</v>
       </c>
       <c r="R23" t="n">
-        <v>6749211</v>
+        <v>6749172</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3520,7 +3520,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124081914</v>
+        <v>124082731</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3576,10 +3576,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623277</v>
+        <v>623207</v>
       </c>
       <c r="R24" t="n">
-        <v>6749287</v>
+        <v>6749191</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -950,7 +950,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124082081</v>
+        <v>124082776</v>
       </c>
       <c r="B4" t="n">
         <v>98101</v>
@@ -985,7 +985,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1002,14 +1002,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Homaren, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623367</v>
+        <v>623214</v>
       </c>
       <c r="R4" t="n">
-        <v>6749289</v>
+        <v>6749211</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1079,7 +1079,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124082864</v>
+        <v>124081914</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,14 +1131,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Vreten, Säljemar, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623224</v>
+        <v>623277</v>
       </c>
       <c r="R5" t="n">
-        <v>6749226</v>
+        <v>6749287</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1170,17 +1170,17 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
           <t>12:00</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1208,7 +1208,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124082507</v>
+        <v>124082802</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1243,7 +1243,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,10 +1264,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623312</v>
+        <v>623221</v>
       </c>
       <c r="R6" t="n">
-        <v>6749173</v>
+        <v>6749218</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1337,7 +1337,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124081914</v>
+        <v>124082242</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1389,14 +1389,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623277</v>
+        <v>623464</v>
       </c>
       <c r="R7" t="n">
-        <v>6749287</v>
+        <v>6749273</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1466,10 +1466,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124081547</v>
+        <v>124082656</v>
       </c>
       <c r="B8" t="n">
-        <v>91030</v>
+        <v>98101</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1478,38 +1478,43 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1517,10 +1522,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623297</v>
+        <v>623245</v>
       </c>
       <c r="R8" t="n">
-        <v>6749278</v>
+        <v>6749178</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1547,22 +1552,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1719,10 +1724,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124082290</v>
+        <v>124081656</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1731,54 +1736,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623462</v>
+        <v>623335</v>
       </c>
       <c r="R10" t="n">
-        <v>6749264</v>
+        <v>6749272</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1848,10 +1848,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124081656</v>
+        <v>124082864</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1860,49 +1860,54 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Vreten, Säljemar, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623335</v>
+        <v>623224</v>
       </c>
       <c r="R11" t="n">
-        <v>6749272</v>
+        <v>6749226</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1934,7 +1939,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1944,7 +1949,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1972,7 +1977,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124082364</v>
+        <v>124082081</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -2024,14 +2029,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623436</v>
+        <v>623367</v>
       </c>
       <c r="R12" t="n">
-        <v>6749241</v>
+        <v>6749289</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2101,7 +2106,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124082323</v>
+        <v>124082290</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2136,7 +2141,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2157,10 +2162,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623457</v>
+        <v>623462</v>
       </c>
       <c r="R13" t="n">
-        <v>6749259</v>
+        <v>6749264</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2230,10 +2235,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124082802</v>
+        <v>124081547</v>
       </c>
       <c r="B14" t="n">
-        <v>98101</v>
+        <v>91030</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2242,43 +2247,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5432</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
@@ -2286,10 +2286,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623221</v>
+        <v>623297</v>
       </c>
       <c r="R14" t="n">
-        <v>6749218</v>
+        <v>6749278</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2316,22 +2316,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2359,7 +2359,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124082677</v>
+        <v>124082507</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623221</v>
+        <v>623312</v>
       </c>
       <c r="R15" t="n">
-        <v>6749177</v>
+        <v>6749173</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124081858</v>
+        <v>124082677</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2544,10 +2544,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623259</v>
+        <v>623221</v>
       </c>
       <c r="R16" t="n">
-        <v>6749292</v>
+        <v>6749177</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2617,7 +2617,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124082656</v>
+        <v>124082422</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2669,14 +2669,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623245</v>
+        <v>623429</v>
       </c>
       <c r="R17" t="n">
-        <v>6749178</v>
+        <v>6749238</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2746,7 +2746,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124082629</v>
+        <v>124081970</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2802,10 +2802,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623266</v>
+        <v>623294</v>
       </c>
       <c r="R18" t="n">
-        <v>6749179</v>
+        <v>6749289</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124081970</v>
+        <v>124082364</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2927,14 +2927,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623294</v>
+        <v>623436</v>
       </c>
       <c r="R19" t="n">
-        <v>6749289</v>
+        <v>6749241</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3004,7 +3004,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124082242</v>
+        <v>124081858</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3056,14 +3056,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623464</v>
+        <v>623259</v>
       </c>
       <c r="R20" t="n">
-        <v>6749273</v>
+        <v>6749292</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3133,7 +3133,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124082776</v>
+        <v>124082534</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623214</v>
+        <v>623302</v>
       </c>
       <c r="R21" t="n">
-        <v>6749211</v>
+        <v>6749172</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3262,7 +3262,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124082422</v>
+        <v>124082731</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3314,14 +3314,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623429</v>
+        <v>623207</v>
       </c>
       <c r="R22" t="n">
-        <v>6749238</v>
+        <v>6749191</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124082534</v>
+        <v>124082629</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3447,10 +3447,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623302</v>
+        <v>623266</v>
       </c>
       <c r="R23" t="n">
-        <v>6749172</v>
+        <v>6749179</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3520,7 +3520,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124082731</v>
+        <v>124082323</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3572,14 +3572,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623207</v>
+        <v>623457</v>
       </c>
       <c r="R24" t="n">
-        <v>6749191</v>
+        <v>6749259</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -950,10 +950,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124082776</v>
+        <v>124081656</v>
       </c>
       <c r="B4" t="n">
-        <v>98101</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -962,43 +962,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr"/>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1006,10 +1001,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623214</v>
+        <v>623335</v>
       </c>
       <c r="R4" t="n">
-        <v>6749211</v>
+        <v>6749272</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1051,7 +1046,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1079,7 +1074,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124081914</v>
+        <v>124082323</v>
       </c>
       <c r="B5" t="n">
         <v>98101</v>
@@ -1114,7 +1109,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,14 +1126,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623277</v>
+        <v>623457</v>
       </c>
       <c r="R5" t="n">
-        <v>6749287</v>
+        <v>6749259</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1208,7 +1203,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124082802</v>
+        <v>124082534</v>
       </c>
       <c r="B6" t="n">
         <v>98101</v>
@@ -1243,7 +1238,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1264,10 +1259,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623221</v>
+        <v>623302</v>
       </c>
       <c r="R6" t="n">
-        <v>6749218</v>
+        <v>6749172</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1337,7 +1332,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124082242</v>
+        <v>124082731</v>
       </c>
       <c r="B7" t="n">
         <v>98101</v>
@@ -1372,7 +1367,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1389,14 +1384,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623464</v>
+        <v>623207</v>
       </c>
       <c r="R7" t="n">
-        <v>6749273</v>
+        <v>6749191</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1466,7 +1461,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124082656</v>
+        <v>124082776</v>
       </c>
       <c r="B8" t="n">
         <v>98101</v>
@@ -1501,7 +1496,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1522,10 +1517,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623245</v>
+        <v>623214</v>
       </c>
       <c r="R8" t="n">
-        <v>6749178</v>
+        <v>6749211</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1595,7 +1590,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124082466</v>
+        <v>124082290</v>
       </c>
       <c r="B9" t="n">
         <v>98101</v>
@@ -1630,7 +1625,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1647,14 +1642,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623332</v>
+        <v>623462</v>
       </c>
       <c r="R9" t="n">
-        <v>6749186</v>
+        <v>6749264</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1724,10 +1719,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124081656</v>
+        <v>124081970</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>98101</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1736,38 +1731,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623335</v>
+        <v>623294</v>
       </c>
       <c r="R10" t="n">
-        <v>6749272</v>
+        <v>6749289</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1848,7 +1848,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124082864</v>
+        <v>124082677</v>
       </c>
       <c r="B11" t="n">
         <v>98101</v>
@@ -1900,14 +1900,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Vreten, Säljemar, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623224</v>
+        <v>623221</v>
       </c>
       <c r="R11" t="n">
-        <v>6749226</v>
+        <v>6749177</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1939,17 +1939,17 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
           <t>12:00</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>12:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1977,7 +1977,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124082081</v>
+        <v>124082507</v>
       </c>
       <c r="B12" t="n">
         <v>98101</v>
@@ -2029,14 +2029,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Homaren, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623367</v>
+        <v>623312</v>
       </c>
       <c r="R12" t="n">
-        <v>6749289</v>
+        <v>6749173</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124082290</v>
+        <v>124082364</v>
       </c>
       <c r="B13" t="n">
         <v>98101</v>
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623462</v>
+        <v>623436</v>
       </c>
       <c r="R13" t="n">
-        <v>6749264</v>
+        <v>6749241</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2359,7 +2359,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124082507</v>
+        <v>124082656</v>
       </c>
       <c r="B15" t="n">
         <v>98101</v>
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623312</v>
+        <v>623245</v>
       </c>
       <c r="R15" t="n">
-        <v>6749173</v>
+        <v>6749178</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2488,7 +2488,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124082677</v>
+        <v>124082081</v>
       </c>
       <c r="B16" t="n">
         <v>98101</v>
@@ -2523,7 +2523,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2540,14 +2540,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Homaren, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623221</v>
+        <v>623367</v>
       </c>
       <c r="R16" t="n">
-        <v>6749177</v>
+        <v>6749289</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2617,7 +2617,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124082422</v>
+        <v>124081858</v>
       </c>
       <c r="B17" t="n">
         <v>98101</v>
@@ -2652,7 +2652,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2669,14 +2669,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623429</v>
+        <v>623259</v>
       </c>
       <c r="R17" t="n">
-        <v>6749238</v>
+        <v>6749292</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2746,7 +2746,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124081970</v>
+        <v>124081914</v>
       </c>
       <c r="B18" t="n">
         <v>98101</v>
@@ -2781,7 +2781,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2802,10 +2802,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623294</v>
+        <v>623277</v>
       </c>
       <c r="R18" t="n">
-        <v>6749289</v>
+        <v>6749287</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2875,7 +2875,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124082364</v>
+        <v>124082802</v>
       </c>
       <c r="B19" t="n">
         <v>98101</v>
@@ -2910,7 +2910,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2927,14 +2927,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>623436</v>
+        <v>623221</v>
       </c>
       <c r="R19" t="n">
-        <v>6749241</v>
+        <v>6749218</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -3004,7 +3004,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124081858</v>
+        <v>124082422</v>
       </c>
       <c r="B20" t="n">
         <v>98101</v>
@@ -3039,7 +3039,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3056,14 +3056,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623259</v>
+        <v>623429</v>
       </c>
       <c r="R20" t="n">
-        <v>6749292</v>
+        <v>6749238</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3133,7 +3133,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124082534</v>
+        <v>124082466</v>
       </c>
       <c r="B21" t="n">
         <v>98101</v>
@@ -3168,7 +3168,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -3189,10 +3189,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623302</v>
+        <v>623332</v>
       </c>
       <c r="R21" t="n">
-        <v>6749172</v>
+        <v>6749186</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3262,7 +3262,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124082731</v>
+        <v>124082242</v>
       </c>
       <c r="B22" t="n">
         <v>98101</v>
@@ -3297,7 +3297,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -3314,14 +3314,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623207</v>
+        <v>623464</v>
       </c>
       <c r="R22" t="n">
-        <v>6749191</v>
+        <v>6749273</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3391,7 +3391,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>124082629</v>
+        <v>124082864</v>
       </c>
       <c r="B23" t="n">
         <v>98101</v>
@@ -3426,7 +3426,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -3443,14 +3443,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Vreten, Säljemar, Gstr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>623266</v>
+        <v>623224</v>
       </c>
       <c r="R23" t="n">
-        <v>6749179</v>
+        <v>6749226</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3520,7 +3520,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>124082323</v>
+        <v>124082629</v>
       </c>
       <c r="B24" t="n">
         <v>98101</v>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -3572,14 +3572,14 @@
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Säljemar Södra, Gstr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>623457</v>
+        <v>623266</v>
       </c>
       <c r="R24" t="n">
-        <v>6749259</v>
+        <v>6749179</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>123957406</v>
       </c>
       <c r="B2" t="n">
-        <v>57513</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -735,7 +730,7 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123957406</v>
       </c>
       <c r="B2" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123957406</v>
       </c>
       <c r="B2" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123957406</v>
       </c>
       <c r="B2" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123957406</v>
       </c>
       <c r="B2" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123957406</v>
       </c>
       <c r="B2" t="n">
-        <v>57892</v>
+        <v>57898</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123957406</v>
       </c>
       <c r="B2" t="n">
-        <v>57898</v>
+        <v>57899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123957406</v>
       </c>
       <c r="B2" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123957406</v>
       </c>
       <c r="B2" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123957406</v>
+        <v>123957350</v>
       </c>
       <c r="B2" t="n">
-        <v>57907</v>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,58 +686,45 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Storhällan, Iggön, Gstr</t>
+          <t>Kapellskär, Gstr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>623479</v>
+        <v>623413</v>
       </c>
       <c r="R2" t="n">
-        <v>6749283</v>
+        <v>6749307</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -767,29 +754,45 @@
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11:30</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-04-10</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrträd</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Fruktkropparna ca 10 meter upp</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Fruktkropparna ca 10 meter upp</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -806,15 +809,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123957350</v>
+        <v>124081656</v>
       </c>
       <c r="B3" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -822,21 +820,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -846,21 +844,21 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kapellskär, Gstr</t>
+          <t>Homaren, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>623413</v>
+        <v>623335</v>
       </c>
       <c r="R3" t="n">
-        <v>6749307</v>
+        <v>6749272</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,12 +885,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,31 +912,6 @@
       <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>Barrträd</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>Fruktkropparna ca 10 meter upp</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Fruktkropparna ca 10 meter upp</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -945,15 +928,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>124081656</v>
+        <v>123957406</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,45 +939,58 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>623335</v>
+        <v>623479</v>
       </c>
       <c r="R4" t="n">
-        <v>6749272</v>
+        <v>6749283</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -1026,22 +1017,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1050,7 +1041,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1069,15 +1059,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>124082323</v>
+        <v>124081858</v>
       </c>
       <c r="B5" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1089,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1121,14 +1106,14 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>623457</v>
+        <v>623259</v>
       </c>
       <c r="R5" t="n">
-        <v>6749259</v>
+        <v>6749292</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1170,7 +1155,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1198,15 +1183,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>124082534</v>
+        <v>124081914</v>
       </c>
       <c r="B6" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,7 +1213,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>200</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1250,14 +1230,14 @@
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Homaren, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>623302</v>
+        <v>623277</v>
       </c>
       <c r="R6" t="n">
-        <v>6749172</v>
+        <v>6749287</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1327,15 +1307,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>124082731</v>
+        <v>124081970</v>
       </c>
       <c r="B7" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1362,7 +1337,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1379,14 +1354,14 @@
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Homaren, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>623207</v>
+        <v>623294</v>
       </c>
       <c r="R7" t="n">
-        <v>6749191</v>
+        <v>6749289</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1456,15 +1431,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124082776</v>
+        <v>124082081</v>
       </c>
       <c r="B8" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1491,7 +1461,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1508,14 +1478,14 @@
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Homaren, Gstr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>623214</v>
+        <v>623367</v>
       </c>
       <c r="R8" t="n">
-        <v>6749211</v>
+        <v>6749289</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1585,15 +1555,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124082290</v>
+        <v>124082242</v>
       </c>
       <c r="B9" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1620,7 +1585,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1637,14 +1602,14 @@
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>623462</v>
+        <v>623464</v>
       </c>
       <c r="R9" t="n">
-        <v>6749264</v>
+        <v>6749273</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1714,15 +1679,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>124081970</v>
+        <v>124082290</v>
       </c>
       <c r="B10" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1749,7 +1709,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1766,14 +1726,14 @@
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>623294</v>
+        <v>623462</v>
       </c>
       <c r="R10" t="n">
-        <v>6749289</v>
+        <v>6749264</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1843,15 +1803,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>124082677</v>
+        <v>124082323</v>
       </c>
       <c r="B11" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1895,14 +1850,14 @@
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>623221</v>
+        <v>623457</v>
       </c>
       <c r="R11" t="n">
-        <v>6749177</v>
+        <v>6749259</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1972,15 +1927,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>124082507</v>
+        <v>124082364</v>
       </c>
       <c r="B12" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2024,14 +1974,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>623312</v>
+        <v>623436</v>
       </c>
       <c r="R12" t="n">
-        <v>6749173</v>
+        <v>6749241</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -2101,15 +2051,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>124082364</v>
+        <v>124082422</v>
       </c>
       <c r="B13" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2136,7 +2081,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -2153,14 +2098,14 @@
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Storhällan, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>623436</v>
+        <v>623429</v>
       </c>
       <c r="R13" t="n">
-        <v>6749241</v>
+        <v>6749238</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2230,61 +2175,61 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>124081547</v>
+        <v>124082466</v>
       </c>
       <c r="B14" t="n">
-        <v>91030</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5432</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Homaren, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>623297</v>
+        <v>623332</v>
       </c>
       <c r="R14" t="n">
-        <v>6749278</v>
+        <v>6749186</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2311,22 +2256,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-04-13</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2354,15 +2299,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>124082656</v>
+        <v>124082507</v>
       </c>
       <c r="B15" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2406,14 +2346,14 @@
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Homaren, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>623245</v>
+        <v>623312</v>
       </c>
       <c r="R15" t="n">
-        <v>6749178</v>
+        <v>6749173</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2483,15 +2423,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>124082081</v>
+        <v>124082534</v>
       </c>
       <c r="B16" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2518,7 +2453,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2535,14 +2470,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Homaren, Gstr</t>
+          <t>Homaren, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>623367</v>
+        <v>623302</v>
       </c>
       <c r="R16" t="n">
-        <v>6749289</v>
+        <v>6749172</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2612,15 +2547,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>124081858</v>
+        <v>124082629</v>
       </c>
       <c r="B17" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2647,7 +2577,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2664,14 +2594,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Homaren, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>623259</v>
+        <v>623266</v>
       </c>
       <c r="R17" t="n">
-        <v>6749292</v>
+        <v>6749179</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2713,7 +2643,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2741,15 +2671,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>124081914</v>
+        <v>124082656</v>
       </c>
       <c r="B18" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2776,7 +2701,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2793,14 +2718,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Homaren, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>623277</v>
+        <v>623245</v>
       </c>
       <c r="R18" t="n">
-        <v>6749287</v>
+        <v>6749178</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2870,15 +2795,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>124082802</v>
+        <v>124082677</v>
       </c>
       <c r="B19" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2922,14 +2842,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Homaren, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q19" t="n">
         <v>623221</v>
       </c>
       <c r="R19" t="n">
-        <v>6749218</v>
+        <v>6749177</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2999,15 +2919,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>124082422</v>
+        <v>124082731</v>
       </c>
       <c r="B20" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3034,7 +2949,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -3051,14 +2966,14 @@
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>623429</v>
+        <v>623207</v>
       </c>
       <c r="R20" t="n">
-        <v>6749238</v>
+        <v>6749191</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -3128,15 +3043,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>124082466</v>
+        <v>124082776</v>
       </c>
       <c r="B21" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3180,14 +3090,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
+          <t>Homaren, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>623332</v>
+        <v>623214</v>
       </c>
       <c r="R21" t="n">
-        <v>6749186</v>
+        <v>6749211</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -3257,15 +3167,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>124082242</v>
+        <v>124082802</v>
       </c>
       <c r="B22" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3309,14 +3214,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Storhällan, Säljemar Södra, Gstr</t>
+          <t>Homaren, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>623464</v>
+        <v>623221</v>
       </c>
       <c r="R22" t="n">
-        <v>6749273</v>
+        <v>6749218</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3389,12 +3294,7 @@
         <v>124082864</v>
       </c>
       <c r="B23" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3438,7 +3338,7 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Vreten, Säljemar, Gstr</t>
+          <t>Vreten, Iggön, Gstr</t>
         </is>
       </c>
       <c r="Q23" t="n">
@@ -3512,135 +3412,6 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>124082629</v>
-      </c>
-      <c r="B24" t="n">
-        <v>98101</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Homaren, Säljemar Södra, Gstr</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>623266</v>
-      </c>
-      <c r="R24" t="n">
-        <v>6749179</v>
-      </c>
-      <c r="S24" t="n">
-        <v>5</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Gävleborg</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Gävle</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Gästrikland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Hille</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:00</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2025-04-13</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF24" t="inlineStr"/>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Petter  Hillborg</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Petter  Hillborg</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 9570-2025 artfynd.xlsx
+++ b/artfynd/A 9570-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -806,6 +811,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123957350</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -925,6 +935,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124081656</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1056,6 +1071,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123957406</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1180,6 +1200,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124081858</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1304,6 +1329,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124081914</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1428,6 +1458,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124081970</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1552,6 +1587,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124082081</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1676,6 +1716,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124082242</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1800,6 +1845,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124082290</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1924,6 +1974,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124082323</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2048,6 +2103,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124082364</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2172,6 +2232,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124082422</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2296,6 +2361,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124082466</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2420,6 +2490,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124082507</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2544,6 +2619,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124082534</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2668,6 +2748,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124082629</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2792,6 +2877,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124082656</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2916,6 +3006,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124082677</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3040,6 +3135,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124082731</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3164,6 +3264,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124082776</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3288,6 +3393,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124082802</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3412,8 +3522,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124082864</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>